--- a/文档/资源.xlsx
+++ b/文档/资源.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Admin\Documents\GitHub\Sistine_civ6mod\文档\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="149">
   <si>
     <t>Civ1</t>
   </si>
@@ -301,6 +306,9 @@
   </si>
   <si>
     <t>RESOURCE_SALT</t>
+  </si>
+  <si>
+    <t>1粮2金</t>
   </si>
   <si>
     <t>0/-1/-2</t>
@@ -484,14 +492,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -970,133 +971,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1107,28 +1108,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2189,16 +2190,16 @@
         <v>21</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="7"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
         <v>54</v>
@@ -2222,13 +2223,13 @@
         <v>61</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q28" s="7"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
         <v>54</v>
@@ -2237,7 +2238,7 @@
         <v>65</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>57</v>
@@ -2246,19 +2247,19 @@
         <v>58</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>14</v>
@@ -2282,7 +2283,7 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
         <v>54</v>
@@ -2303,13 +2304,13 @@
         <v>15</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q31" s="7"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
@@ -2327,7 +2328,7 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
@@ -2342,13 +2343,13 @@
         <v>70</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q33" s="7"/>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
@@ -2360,29 +2361,29 @@
         <v>15</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q34" s="7"/>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>74</v>
@@ -2397,7 +2398,7 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
@@ -2421,13 +2422,13 @@
         <v>15</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q36" s="7"/>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
@@ -2439,13 +2440,13 @@
         <v>61</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q37" s="7"/>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
@@ -2463,7 +2464,7 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
         <v>54</v>
@@ -2475,13 +2476,13 @@
         <v>88</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q39" s="7"/>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -2499,46 +2500,46 @@
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>87</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O41" s="6"/>
       <c r="Q41" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>32</v>
@@ -2547,7 +2548,7 @@
         <v>33</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>15</v>
@@ -2557,13 +2558,13 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>65</v>
@@ -2572,10 +2573,10 @@
         <v>32</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>15</v>
@@ -2585,10 +2586,10 @@
     </row>
     <row r="44" spans="1:17">
       <c r="A44" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>50</v>
@@ -2606,23 +2607,23 @@
         <v>87</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O44" s="6"/>
       <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>65</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>15</v>
@@ -2632,25 +2633,25 @@
     </row>
     <row r="46" spans="1:17">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>50</v>
@@ -2663,22 +2664,22 @@
     </row>
     <row r="47" spans="1:17">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>15</v>
@@ -2688,7 +2689,7 @@
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>77</v>
@@ -2703,18 +2704,18 @@
         <v>65</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" ht="70.8" customHeight="1" spans="1:5">
       <c r="C49" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" ht="70.8" customHeight="1" spans="1:5">
@@ -2726,7 +2727,7 @@
         <v>19</v>
       </c>
       <c r="B52" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2737,7 +2738,7 @@
         <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -2748,7 +2749,7 @@
         <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -2759,7 +2760,7 @@
         <v>35</v>
       </c>
       <c r="B55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -2770,7 +2771,7 @@
         <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2781,7 +2782,7 @@
         <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -2792,7 +2793,7 @@
         <v>44</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2803,7 +2804,7 @@
         <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2814,7 +2815,7 @@
         <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2825,7 +2826,7 @@
         <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -2836,7 +2837,7 @@
         <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -2847,7 +2848,7 @@
         <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63">
         <v>3</v>
@@ -2858,7 +2859,7 @@
         <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -2869,7 +2870,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C65">
         <v>3</v>
@@ -2880,7 +2881,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C66">
         <v>3</v>
@@ -2891,7 +2892,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -2902,7 +2903,7 @@
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -2913,7 +2914,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -2924,7 +2925,7 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -2935,7 +2936,7 @@
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -2946,7 +2947,7 @@
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -2957,7 +2958,7 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -2968,7 +2969,7 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -2979,7 +2980,7 @@
         <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -2990,7 +2991,7 @@
         <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -3001,7 +3002,7 @@
         <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -3012,7 +3013,7 @@
         <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -3023,7 +3024,7 @@
         <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -3034,7 +3035,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -3042,10 +3043,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -3053,10 +3054,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -3064,10 +3065,10 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -3075,10 +3076,10 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B84" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -3086,10 +3087,10 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B85" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3097,10 +3098,10 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -3108,10 +3109,10 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B87" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C87">
         <v>3</v>
@@ -3119,10 +3120,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B88" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -3130,10 +3131,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B89" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3141,10 +3142,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B90" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -3152,10 +3153,10 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B91" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -3163,10 +3164,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B92" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -3174,10 +3175,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -3185,10 +3186,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B94" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -3196,10 +3197,10 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -3207,10 +3208,10 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B96" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -3218,10 +3219,10 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B97" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -3229,10 +3230,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B98" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -3240,10 +3241,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B99" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C99">
         <v>3</v>
@@ -3251,10 +3252,10 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -3262,10 +3263,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -3273,10 +3274,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B102" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -3284,10 +3285,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B103" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -3295,10 +3296,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B104" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -3309,7 +3310,7 @@
         <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C105">
         <v>2</v>
@@ -3317,10 +3318,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B106" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C106">
         <v>2</v>
